--- a/exploratory_data_analisys/dimensions_reduction/risultati/statistiche_descrittive.xlsx
+++ b/exploratory_data_analisys/dimensions_reduction/risultati/statistiche_descrittive.xlsx
@@ -425,76 +425,71 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O9"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>IslandArea</t>
+          <t>Densità_pop</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Densità_pop</t>
+          <t>evi</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>evi</t>
+          <t>eolico</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>eolico</t>
+          <t>eolico_std</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>eolico_std</t>
+          <t>offshore</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>offshore</t>
+          <t>gdp_pro_capite</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>gdp_pro_capite</t>
+          <t>geothermal_potential</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>geothermal_potential</t>
+          <t>hydro</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>hydro</t>
+          <t>temp</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>temp</t>
+          <t>solar_pow</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>solar_pow</t>
+          <t>solar_seas_ind</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>solar_seas_ind</t>
+          <t>superficie_res</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>superficie_res</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>gdp_pop_urban_merged</t>
         </is>
@@ -545,9 +540,6 @@
       <c r="N2" t="n">
         <v>2736</v>
       </c>
-      <c r="O2" t="n">
-        <v>2736</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -556,46 +548,43 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>320.288530915809</v>
+        <v>178.0707293410548</v>
       </c>
       <c r="C3" t="n">
-        <v>178.0707293410548</v>
+        <v>3291.897765996209</v>
       </c>
       <c r="D3" t="n">
-        <v>3291.897765996209</v>
+        <v>181.8270959321153</v>
       </c>
       <c r="E3" t="n">
-        <v>181.8270959321153</v>
+        <v>0.5146606913250859</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5146606913250859</v>
+        <v>3.58541783710352</v>
       </c>
       <c r="G3" t="n">
-        <v>3.58541783710352</v>
+        <v>20074.87284515543</v>
       </c>
       <c r="H3" t="n">
-        <v>20074.87284515543</v>
+        <v>108.1126096491228</v>
       </c>
       <c r="I3" t="n">
-        <v>108.1126096491228</v>
+        <v>91837287.51608187</v>
       </c>
       <c r="J3" t="n">
-        <v>91837287.51608187</v>
+        <v>22.79750020687123</v>
       </c>
       <c r="K3" t="n">
-        <v>22.79750020687123</v>
+        <v>3.918410325869482</v>
       </c>
       <c r="L3" t="n">
-        <v>3.918410325869482</v>
+        <v>2.770811126158948</v>
       </c>
       <c r="M3" t="n">
-        <v>2.770811126158948</v>
+        <v>89.62701874123194</v>
       </c>
       <c r="N3" t="n">
-        <v>41.5145742480835</v>
-      </c>
-      <c r="O3" t="n">
-        <v>-2.077610338479825e-17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -605,45 +594,42 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2225.638396288761</v>
+        <v>375.9024184178274</v>
       </c>
       <c r="C4" t="n">
-        <v>375.9024184178274</v>
+        <v>1178.978898353756</v>
       </c>
       <c r="D4" t="n">
-        <v>1178.978898353756</v>
+        <v>172.0007794221645</v>
       </c>
       <c r="E4" t="n">
-        <v>172.0007794221645</v>
+        <v>0.1885384736748264</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1885384736748264</v>
+        <v>11.0093836351871</v>
       </c>
       <c r="G4" t="n">
-        <v>11.0093836351871</v>
+        <v>19535.53724536365</v>
       </c>
       <c r="H4" t="n">
-        <v>19535.53724536365</v>
+        <v>2019.256884673575</v>
       </c>
       <c r="I4" t="n">
-        <v>2019.256884673575</v>
+        <v>1790451760.097511</v>
       </c>
       <c r="J4" t="n">
-        <v>1790451760.097511</v>
+        <v>6.815510575137362</v>
       </c>
       <c r="K4" t="n">
-        <v>6.815510575137362</v>
+        <v>0.5827628089251643</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5827628089251643</v>
+        <v>6.210745833011489</v>
       </c>
       <c r="M4" t="n">
-        <v>6.210745833011489</v>
+        <v>780.1182741035933</v>
       </c>
       <c r="N4" t="n">
-        <v>30.60383302137502</v>
-      </c>
-      <c r="O4" t="n">
         <v>1.617025255265242</v>
       </c>
     </row>
@@ -654,45 +640,42 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.02442826156</v>
+        <v>0.03004947825703742</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03004947825703742</v>
+        <v>-204.689456728981</v>
       </c>
       <c r="D5" t="n">
-        <v>-204.689456728981</v>
+        <v>0.1650183725831132</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1650183725831132</v>
+        <v>0.1098023797772846</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1098023797772846</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>577</v>
       </c>
       <c r="H5" t="n">
-        <v>577</v>
+        <v>-7.105427357601002e-14</v>
       </c>
       <c r="I5" t="n">
-        <v>-7.105427357601002e-14</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>-4.84112448167906</v>
       </c>
       <c r="K5" t="n">
-        <v>-4.84112448167906</v>
+        <v>1.647504687309265</v>
       </c>
       <c r="L5" t="n">
-        <v>1.647504687309265</v>
+        <v>1.1138014793396</v>
       </c>
       <c r="M5" t="n">
-        <v>1.1138014793396</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
         <v>-0.36348952643961</v>
       </c>
     </row>
@@ -703,46 +686,43 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10.007699383425</v>
+        <v>24.38240113820417</v>
       </c>
       <c r="C6" t="n">
-        <v>24.38240113820417</v>
+        <v>2429.12666317147</v>
       </c>
       <c r="D6" t="n">
-        <v>2429.12666317147</v>
+        <v>46.12133486670739</v>
       </c>
       <c r="E6" t="n">
-        <v>46.12133486670739</v>
+        <v>0.3733514162194859</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3733514162194859</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>4465</v>
       </c>
       <c r="H6" t="n">
-        <v>4465</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>18.63869539896649</v>
       </c>
       <c r="K6" t="n">
-        <v>18.63869539896649</v>
+        <v>3.637920200824738</v>
       </c>
       <c r="L6" t="n">
-        <v>3.637920200824738</v>
+        <v>1.304867506027222</v>
       </c>
       <c r="M6" t="n">
-        <v>1.304867506027222</v>
+        <v>2.846561352709789</v>
       </c>
       <c r="N6" t="n">
-        <v>15.56122696349549</v>
-      </c>
-      <c r="O6" t="n">
-        <v>-0.3581700869467753</v>
+        <v>-0.3581700869467754</v>
       </c>
     </row>
     <row r="7">
@@ -752,46 +732,43 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>26.36959805225</v>
+        <v>66.17086868870709</v>
       </c>
       <c r="C7" t="n">
-        <v>66.17086868870709</v>
+        <v>3241.854034301131</v>
       </c>
       <c r="D7" t="n">
-        <v>3241.854034301131</v>
+        <v>126.3501521243566</v>
       </c>
       <c r="E7" t="n">
-        <v>126.3501521243566</v>
+        <v>0.5016595630514513</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5016595630514513</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>12025</v>
       </c>
       <c r="H7" t="n">
-        <v>12025</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>26.62771288553876</v>
       </c>
       <c r="K7" t="n">
-        <v>26.62771288553876</v>
+        <v>3.986884474754333</v>
       </c>
       <c r="L7" t="n">
-        <v>3.986884474754333</v>
+        <v>1.462561845779419</v>
       </c>
       <c r="M7" t="n">
-        <v>1.462561845779419</v>
+        <v>7.548455726310969</v>
       </c>
       <c r="N7" t="n">
-        <v>34.20183389023812</v>
-      </c>
-      <c r="O7" t="n">
-        <v>-0.3440510274353928</v>
+        <v>-0.344051027435393</v>
       </c>
     </row>
     <row r="8">
@@ -801,45 +778,42 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>98.32418531425</v>
+        <v>173.8929336902572</v>
       </c>
       <c r="C8" t="n">
-        <v>173.8929336902572</v>
+        <v>4173.546025584545</v>
       </c>
       <c r="D8" t="n">
-        <v>4173.546025584545</v>
+        <v>277.4768353649193</v>
       </c>
       <c r="E8" t="n">
-        <v>277.4768353649193</v>
+        <v>0.6360433029020202</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6360433029020202</v>
+        <v>3.152169036120929</v>
       </c>
       <c r="G8" t="n">
-        <v>3.152169036120929</v>
+        <v>33345.25</v>
       </c>
       <c r="H8" t="n">
-        <v>33345.25</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>78839</v>
       </c>
       <c r="J8" t="n">
-        <v>78839</v>
+        <v>27.45785426272431</v>
       </c>
       <c r="K8" t="n">
-        <v>27.45785426272431</v>
+        <v>4.289039850234985</v>
       </c>
       <c r="L8" t="n">
-        <v>4.289039850234985</v>
+        <v>1.93812695145607</v>
       </c>
       <c r="M8" t="n">
-        <v>1.93812695145607</v>
+        <v>29.11773980316483</v>
       </c>
       <c r="N8" t="n">
-        <v>66.15938527126622</v>
-      </c>
-      <c r="O8" t="n">
         <v>-0.2768307385759184</v>
       </c>
     </row>
@@ -850,46 +824,43 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>74237.1104743</v>
+        <v>8700.31031846173</v>
       </c>
       <c r="C9" t="n">
-        <v>8700.31031846173</v>
+        <v>6361.518912937679</v>
       </c>
       <c r="D9" t="n">
-        <v>6361.518912937679</v>
+        <v>919.7850914712542</v>
       </c>
       <c r="E9" t="n">
-        <v>919.7850914712542</v>
+        <v>1.63834005044413</v>
       </c>
       <c r="F9" t="n">
-        <v>1.63834005044413</v>
+        <v>232.3907979412545</v>
       </c>
       <c r="G9" t="n">
-        <v>232.3907979412545</v>
+        <v>144634.4446974098</v>
       </c>
       <c r="H9" t="n">
-        <v>144634.4446974098</v>
+        <v>103215.4</v>
       </c>
       <c r="I9" t="n">
-        <v>103215.4</v>
+        <v>80448079491</v>
       </c>
       <c r="J9" t="n">
-        <v>80448079491</v>
+        <v>29.71450203074806</v>
       </c>
       <c r="K9" t="n">
-        <v>29.71450203074806</v>
+        <v>5.415648937225342</v>
       </c>
       <c r="L9" t="n">
-        <v>5.415648937225342</v>
+        <v>195.6085052490234</v>
       </c>
       <c r="M9" t="n">
-        <v>195.6085052490234</v>
+        <v>33916.71640912977</v>
       </c>
       <c r="N9" t="n">
-        <v>100</v>
-      </c>
-      <c r="O9" t="n">
-        <v>26.14180082354962</v>
+        <v>26.14180082354963</v>
       </c>
     </row>
   </sheetData>
